--- a/isms-core-framework/A.8-technological-controls/isms-a.8.10-data-deletion/WKBK/90_workbooks/ISMS-IMP-A.8.10.3_Third_Party_Cloud_Deletion_20260208.xlsx
+++ b/isms-core-framework/A.8-technological-controls/isms-a.8.10-data-deletion/WKBK/90_workbooks/ISMS-IMP-A.8.10.3_Third_Party_Cloud_Deletion_20260208.xlsx
@@ -3824,7 +3824,7 @@
       </c>
       <c r="B53" s="14" t="inlineStr">
         <is>
-          <t>Secure deletion per NIST SP 800-88</t>
+          <t>Secure deletion per NIST SP 800-88 Rev. 2</t>
         </is>
       </c>
     </row>
